--- a/SourceData_SV2A.xlsx
+++ b/SourceData_SV2A.xlsx
@@ -14,7 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extended Data 1 (AD)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extended Data 2" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extended Data 3" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extended Data 1 (AD)" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A106"/>
+  <dimension ref="A1:A135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -743,417 +746,3206 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>NOT INCLUDED (data held outside the Prism analysis files)</t>
+          <t>5xFAD COHORT (Figure 7, Extended Data 2 and 3)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Figure 7 — 5xFAD behaviour / Barnes maze</t>
+          <t xml:space="preserve">  From the 'AD' folder: OFT baseline and repeat 2, Barnes repeat 2,</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Extended Data (OLT/NOR, Barnes), Supplementary Figure 1</t>
+          <t xml:space="preserve">  NORT repeat 2 and OLT repeat 2 Prism files.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Groups are WT (or WT-Sham/WT-Ctrl), 5xFAD-EGFP and 5xFAD-SV2A,</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>CONTENTS</t>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  in that column order. Fig 7a is the two-group WT vs 5xFAD baseline.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Figure 1</t>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  n = 10 WT-Ctrl, 5 5xFAD-EGFP, 9 5xFAD-SV2A in the Barnes maze; two</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">      j   SV2A-positive cell density (cells/mm2) by hippocampal region</t>
+          <t xml:space="preserve">  5xFAD-EGFP animals were lost between the recognition tasks and the</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">      k   SV2A immunoreactivity, mean grey value, by hippocampal region</t>
+          <t xml:space="preserve">  Barnes maze.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Figure 2</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      c   sIPSC / mIPSC frequency (Hz)</t>
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>NOT INCLUDED</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Supplementary Figure 1 (NED-Net validation).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>CONTENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Figure 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      j   SV2A-positive cell density (cells/mm2) by hippocampal region</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      k   SV2A immunoreactivity, mean grey value, by hippocampal region</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Figure 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      c   sIPSC / mIPSC frequency (Hz)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">      d   sIPSC inter-event interval, cumulative distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      e   mIPSC inter-event interval, cumulative distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      f   sIPSC / mIPSC amplitude (pA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      g   sIPSC amplitude, cumulative distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      h   mIPSC amplitude, cumulative distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      i   sIPSC / mIPSC rise time (ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      j   sIPSC rise time, cumulative distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      k   mIPSC rise time, cumulative distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Figure 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      c   Seizures per 24 h of recording, baseline (weeks 1-3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      d   % of recorded days without a convulsive seizure, baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      e   All seizures per 24 h, by baseline week</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      f   Time to first convulsive seizure, baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      g   Cumulative convulsive seizure burden (min), baseline days 1-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      h   Mean seizure duration (s), whole recording</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      i   Average behavioural seizure grade during status epilepticus</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      j   Cumulative behavioural seizure grade during SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      k   Cumulative SE grade vs chronic seizure rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Figure 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      c   Interictal spikes per animal-hour, baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      d   Mean interictal spike duration (s), baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      e   Inter-spike-interval probability density (ISIs pooled within group)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      f   Inter-spike-interval cumulative distribution (pooled within group)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Figure 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      a   All seizures per animal-hour, by recording day</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      b   % days convulsive-free, baseline vs levetiracetam</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      c   Convulsive seizures per 24 h, baseline vs levetiracetam</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      d   Non-convulsive seizures per 24 h, baseline vs levetiracetam</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      e   Mean convulsive seizure duration (s), baseline vs levetiracetam</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      f   Mean non-convulsive seizure duration (s), baseline vs levetiracetam</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      g   Interictal spikes per animal-hour, baseline vs levetiracetam</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      h   ISI cumulative distribution, EGFP, baseline vs LEV</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      h   ISI cumulative distribution, SV2A, baseline vs LEV</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      i   Mean spike duration (s), baseline vs levetiracetam</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Figure 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      b   Object location test — exploration time (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      c   Object location test — head entries</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      d   Object location test — discrimination index</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      f   Novel object recognition — exploration time (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      g   Novel object recognition — head entries</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      h   Novel object recognition — discrimination index</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      j   Nest-building score (Deacon protocol)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      l   Open field — time mobile (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      m   Open field — centre entries</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      n   Open field — time in centre (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      o   Open field — time in centre (% of mobile time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Figure 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      a   Open field distance (m), WT vs 5xFAD at baseline (2 columns)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      b   Open field distance (m) after treatment (columns: WT, 5xFAD-EGFP, 5xFAD-SV2A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      c   Time in centre (fraction of total), pre vs post treatment (rows Pre/Post; columns are animals, WT then 5xFAD-EGFP then 5xFAD-SV2A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      d   Barnes maze, change in AUC of primary latency</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      e   Barnes maze, change in AUC of total latency</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      f   Barnes maze, change in AUC of total errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Extended Data 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      a   Object location: exploration time (s), familiar vs displaced</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      b   Object location: head entries, familiar vs displaced</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      c   Object location: discrimination index (columns: WT-Sham, 5xFAD-EGFP, 5xFAD-SV2A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      d   Novel object: exploration time (s), familiar vs novel</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      e   Novel object: head entries, familiar vs novel</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      f   Novel object: discrimination index (columns: WT-Sham, 5xFAD-EGFP, 5xFAD-SV2A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Extended Data 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      a   Barnes maze training: primary latency (s), rows = trials 1-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      b   Barnes maze training: total latency (s), rows = trials 1-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      c   Barnes maze training: primary errors, rows = trials 1-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      d   Barnes maze training: total errors, rows = trials 1-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      e   Barnes maze probe trial: latency (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      f   Barnes maze probe trial: errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Extended Data 1 (AD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      c   Interictal spikes per animal-hour, by recording day (col 1 = day, then animals 1-4, then cohort mean)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      d   Interictal spikes per animal-hour, by week (rows = animals 1-4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      -   Seizures detected in the AD cohort (not plotted; quoted in the text)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AE68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Extended Data 3a — Barnes maze training: primary latency (s), rows = trials 1-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Statistical test: Two-way ANOVA with Dunnett's multiple comparisons</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Row = condition/trial; values are individual animals, WT, then 5xFAD-EGFP, then 5xFAD-SV2A, in the order plotted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>58</v>
+      </c>
+      <c r="C4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F4" t="n">
+        <v>32</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>96</v>
+      </c>
+      <c r="L4" t="n">
+        <v>20</v>
+      </c>
+      <c r="M4" t="n">
+        <v>24</v>
+      </c>
+      <c r="N4" t="n">
+        <v>58</v>
+      </c>
+      <c r="O4" t="n">
+        <v>152</v>
+      </c>
+      <c r="P4" t="n">
+        <v>156</v>
+      </c>
+      <c r="V4" t="n">
+        <v>21</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E5" t="n">
+        <v>37</v>
+      </c>
+      <c r="F5" t="n">
+        <v>29</v>
+      </c>
+      <c r="G5" t="n">
+        <v>51</v>
+      </c>
+      <c r="H5" t="n">
+        <v>27</v>
+      </c>
+      <c r="I5" t="n">
+        <v>47</v>
+      </c>
+      <c r="J5" t="n">
+        <v>44</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86</v>
+      </c>
+      <c r="L5" t="n">
+        <v>155</v>
+      </c>
+      <c r="M5" t="n">
+        <v>55</v>
+      </c>
+      <c r="N5" t="n">
+        <v>171</v>
+      </c>
+      <c r="O5" t="n">
+        <v>112</v>
+      </c>
+      <c r="P5" t="n">
+        <v>35</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6</v>
+      </c>
+      <c r="W5" t="n">
+        <v>43</v>
+      </c>
+      <c r="X5" t="n">
+        <v>128</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>169</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>62</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C6" t="n">
+        <v>34</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>85</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>57</v>
+      </c>
+      <c r="L6" t="n">
+        <v>43</v>
+      </c>
+      <c r="M6" t="n">
+        <v>18</v>
+      </c>
+      <c r="N6" t="n">
+        <v>17</v>
+      </c>
+      <c r="O6" t="n">
+        <v>102</v>
+      </c>
+      <c r="P6" t="n">
+        <v>44</v>
+      </c>
+      <c r="V6" t="n">
+        <v>16</v>
+      </c>
+      <c r="W6" t="n">
+        <v>48</v>
+      </c>
+      <c r="X6" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>69</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>24</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>19</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>31</v>
+      </c>
+      <c r="I7" t="n">
+        <v>16</v>
+      </c>
+      <c r="J7" t="n">
+        <v>26</v>
+      </c>
+      <c r="K7" t="n">
+        <v>11</v>
+      </c>
+      <c r="L7" t="n">
+        <v>45</v>
+      </c>
+      <c r="M7" t="n">
+        <v>26</v>
+      </c>
+      <c r="N7" t="n">
+        <v>149</v>
+      </c>
+      <c r="O7" t="n">
+        <v>25</v>
+      </c>
+      <c r="P7" t="n">
+        <v>69</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6</v>
+      </c>
+      <c r="W7" t="n">
+        <v>58</v>
+      </c>
+      <c r="X7" t="n">
+        <v>117</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>37</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G8" t="n">
+        <v>11</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>53</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11</v>
+      </c>
+      <c r="K8" t="n">
+        <v>13</v>
+      </c>
+      <c r="L8" t="n">
+        <v>40</v>
+      </c>
+      <c r="M8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N8" t="n">
+        <v>159</v>
+      </c>
+      <c r="O8" t="n">
+        <v>10</v>
+      </c>
+      <c r="P8" t="n">
+        <v>23</v>
+      </c>
+      <c r="V8" t="n">
+        <v>20</v>
+      </c>
+      <c r="W8" t="n">
+        <v>115</v>
+      </c>
+      <c r="X8" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>69</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>37</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Extended Data 3b — Barnes maze training: total latency (s), rows = trials 1-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Statistical test: Two-way ANOVA with Dunnett's multiple comparisons</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Row = condition/trial; values are individual animals, WT, then 5xFAD-EGFP, then 5xFAD-SV2A, in the order plotted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>62</v>
+      </c>
+      <c r="C14" t="n">
+        <v>30</v>
+      </c>
+      <c r="D14" t="n">
+        <v>21</v>
+      </c>
+      <c r="E14" t="n">
+        <v>37</v>
+      </c>
+      <c r="F14" t="n">
+        <v>35</v>
+      </c>
+      <c r="G14" t="n">
+        <v>13</v>
+      </c>
+      <c r="H14" t="n">
+        <v>18</v>
+      </c>
+      <c r="I14" t="n">
+        <v>18</v>
+      </c>
+      <c r="J14" t="n">
+        <v>11</v>
+      </c>
+      <c r="K14" t="n">
+        <v>104</v>
+      </c>
+      <c r="L14" t="n">
+        <v>23</v>
+      </c>
+      <c r="M14" t="n">
+        <v>28</v>
+      </c>
+      <c r="N14" t="n">
+        <v>180</v>
+      </c>
+      <c r="O14" t="n">
+        <v>156</v>
+      </c>
+      <c r="P14" t="n">
+        <v>171</v>
+      </c>
+      <c r="V14" t="n">
+        <v>23</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>180</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>34</v>
+      </c>
+      <c r="C15" t="n">
+        <v>19</v>
+      </c>
+      <c r="D15" t="n">
+        <v>36</v>
+      </c>
+      <c r="E15" t="n">
+        <v>40</v>
+      </c>
+      <c r="F15" t="n">
+        <v>31</v>
+      </c>
+      <c r="G15" t="n">
+        <v>53</v>
+      </c>
+      <c r="H15" t="n">
+        <v>34</v>
+      </c>
+      <c r="I15" t="n">
+        <v>51</v>
+      </c>
+      <c r="J15" t="n">
+        <v>47</v>
+      </c>
+      <c r="K15" t="n">
+        <v>91</v>
+      </c>
+      <c r="L15" t="n">
+        <v>156</v>
+      </c>
+      <c r="M15" t="n">
+        <v>56</v>
+      </c>
+      <c r="N15" t="n">
+        <v>180</v>
+      </c>
+      <c r="O15" t="n">
+        <v>113</v>
+      </c>
+      <c r="P15" t="n">
+        <v>180</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7</v>
+      </c>
+      <c r="W15" t="n">
+        <v>46</v>
+      </c>
+      <c r="X15" t="n">
+        <v>131</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>173</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>180</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>22</v>
+      </c>
+      <c r="C16" t="n">
+        <v>36</v>
+      </c>
+      <c r="D16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E16" t="n">
+        <v>98</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9</v>
+      </c>
+      <c r="G16" t="n">
+        <v>7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>28</v>
+      </c>
+      <c r="J16" t="n">
+        <v>9</v>
+      </c>
+      <c r="K16" t="n">
+        <v>64</v>
+      </c>
+      <c r="L16" t="n">
+        <v>47</v>
+      </c>
+      <c r="M16" t="n">
+        <v>19</v>
+      </c>
+      <c r="N16" t="n">
+        <v>28</v>
+      </c>
+      <c r="O16" t="n">
+        <v>104</v>
+      </c>
+      <c r="P16" t="n">
+        <v>55</v>
+      </c>
+      <c r="V16" t="n">
+        <v>17</v>
+      </c>
+      <c r="W16" t="n">
+        <v>53</v>
+      </c>
+      <c r="X16" t="n">
+        <v>66</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>29</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="n">
+        <v>26</v>
+      </c>
+      <c r="F17" t="n">
+        <v>13</v>
+      </c>
+      <c r="G17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" t="n">
+        <v>33</v>
+      </c>
+      <c r="I17" t="n">
+        <v>19</v>
+      </c>
+      <c r="J17" t="n">
+        <v>28</v>
+      </c>
+      <c r="K17" t="n">
+        <v>14</v>
+      </c>
+      <c r="L17" t="n">
+        <v>47</v>
+      </c>
+      <c r="M17" t="n">
+        <v>29</v>
+      </c>
+      <c r="N17" t="n">
+        <v>180</v>
+      </c>
+      <c r="O17" t="n">
+        <v>27</v>
+      </c>
+      <c r="P17" t="n">
+        <v>76</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>67</v>
+      </c>
+      <c r="X17" t="n">
+        <v>122</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>74</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>41</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>180</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>19</v>
+      </c>
+      <c r="E18" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" t="n">
+        <v>18</v>
+      </c>
+      <c r="G18" t="n">
+        <v>18</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>55</v>
+      </c>
+      <c r="J18" t="n">
+        <v>12</v>
+      </c>
+      <c r="K18" t="n">
+        <v>16</v>
+      </c>
+      <c r="L18" t="n">
+        <v>41</v>
+      </c>
+      <c r="M18" t="n">
+        <v>12</v>
+      </c>
+      <c r="N18" t="n">
+        <v>180</v>
+      </c>
+      <c r="O18" t="n">
+        <v>11</v>
+      </c>
+      <c r="P18" t="n">
+        <v>42</v>
+      </c>
+      <c r="V18" t="n">
+        <v>21</v>
+      </c>
+      <c r="W18" t="n">
+        <v>120</v>
+      </c>
+      <c r="X18" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>71</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Extended Data 3c — Barnes maze training: primary errors, rows = trials 1-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Statistical test: Two-way ANOVA with Dunnett's multiple comparisons</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Row = condition/trial; values are individual animals, WT, then 5xFAD-EGFP, then 5xFAD-SV2A, in the order plotted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>18</v>
+      </c>
+      <c r="C24" t="n">
+        <v>7</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15</v>
+      </c>
+      <c r="F24" t="n">
+        <v>12</v>
+      </c>
+      <c r="G24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>23</v>
+      </c>
+      <c r="L24" t="n">
+        <v>11</v>
+      </c>
+      <c r="M24" t="n">
+        <v>6</v>
+      </c>
+      <c r="N24" t="n">
+        <v>15</v>
+      </c>
+      <c r="O24" t="n">
+        <v>17</v>
+      </c>
+      <c r="P24" t="n">
+        <v>22</v>
+      </c>
+      <c r="V24" t="n">
+        <v>11</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>15</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="n">
+        <v>14</v>
+      </c>
+      <c r="F25" t="n">
+        <v>14</v>
+      </c>
+      <c r="G25" t="n">
+        <v>17</v>
+      </c>
+      <c r="H25" t="n">
+        <v>11</v>
+      </c>
+      <c r="I25" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" t="n">
+        <v>13</v>
+      </c>
+      <c r="K25" t="n">
+        <v>23</v>
+      </c>
+      <c r="L25" t="n">
+        <v>29</v>
+      </c>
+      <c r="M25" t="n">
+        <v>21</v>
+      </c>
+      <c r="N25" t="n">
+        <v>5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>11</v>
+      </c>
+      <c r="P25" t="n">
+        <v>5</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>15</v>
+      </c>
+      <c r="X25" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>13</v>
+      </c>
+      <c r="C26" t="n">
+        <v>17</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>14</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" t="n">
+        <v>13</v>
+      </c>
+      <c r="M26" t="n">
+        <v>14</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>13</v>
+      </c>
+      <c r="P26" t="n">
+        <v>4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>11</v>
+      </c>
+      <c r="W26" t="n">
+        <v>17</v>
+      </c>
+      <c r="X26" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>17</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>7</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" t="n">
+        <v>13</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>14</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>13</v>
+      </c>
+      <c r="M27" t="n">
+        <v>17</v>
+      </c>
+      <c r="N27" t="n">
+        <v>6</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2</v>
+      </c>
+      <c r="P27" t="n">
+        <v>9</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>16</v>
+      </c>
+      <c r="X27" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>11</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9</v>
+      </c>
+      <c r="J28" t="n">
+        <v>7</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>14</v>
+      </c>
+      <c r="M28" t="n">
+        <v>8</v>
+      </c>
+      <c r="N28" t="n">
+        <v>6</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2</v>
+      </c>
+      <c r="P28" t="n">
+        <v>4</v>
+      </c>
+      <c r="V28" t="n">
+        <v>11</v>
+      </c>
+      <c r="W28" t="n">
+        <v>24</v>
+      </c>
+      <c r="X28" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Extended Data 3d — Barnes maze training: total errors, rows = trials 1-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Statistical test: Two-way ANOVA with Dunnett's multiple comparisons</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Row = condition/trial; values are individual animals, WT, then 5xFAD-EGFP, then 5xFAD-SV2A, in the order plotted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>19</v>
+      </c>
+      <c r="C34" t="n">
+        <v>7</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>15</v>
+      </c>
+      <c r="F34" t="n">
+        <v>12</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>23</v>
+      </c>
+      <c r="L34" t="n">
+        <v>11</v>
+      </c>
+      <c r="M34" t="n">
+        <v>6</v>
+      </c>
+      <c r="N34" t="n">
+        <v>35</v>
+      </c>
+      <c r="O34" t="n">
+        <v>17</v>
+      </c>
+      <c r="P34" t="n">
+        <v>22</v>
+      </c>
+      <c r="V34" t="n">
+        <v>11</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>15</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="n">
+        <v>14</v>
+      </c>
+      <c r="F35" t="n">
+        <v>14</v>
+      </c>
+      <c r="G35" t="n">
+        <v>17</v>
+      </c>
+      <c r="H35" t="n">
+        <v>11</v>
+      </c>
+      <c r="I35" t="n">
+        <v>10</v>
+      </c>
+      <c r="J35" t="n">
+        <v>13</v>
+      </c>
+      <c r="K35" t="n">
+        <v>23</v>
+      </c>
+      <c r="L35" t="n">
+        <v>29</v>
+      </c>
+      <c r="M35" t="n">
+        <v>21</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6</v>
+      </c>
+      <c r="O35" t="n">
+        <v>11</v>
+      </c>
+      <c r="P35" t="n">
+        <v>24</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>15</v>
+      </c>
+      <c r="X35" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>13</v>
+      </c>
+      <c r="C36" t="n">
+        <v>17</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" t="n">
+        <v>15</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>8</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>10</v>
+      </c>
+      <c r="L36" t="n">
+        <v>13</v>
+      </c>
+      <c r="M36" t="n">
+        <v>14</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" t="n">
+        <v>13</v>
+      </c>
+      <c r="P36" t="n">
+        <v>4</v>
+      </c>
+      <c r="V36" t="n">
+        <v>11</v>
+      </c>
+      <c r="W36" t="n">
+        <v>17</v>
+      </c>
+      <c r="X36" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>17</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F37" t="n">
+        <v>7</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" t="n">
+        <v>13</v>
+      </c>
+      <c r="I37" t="n">
+        <v>5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>14</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4</v>
+      </c>
+      <c r="L37" t="n">
+        <v>13</v>
+      </c>
+      <c r="M37" t="n">
+        <v>17</v>
+      </c>
+      <c r="N37" t="n">
+        <v>9</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2</v>
+      </c>
+      <c r="P37" t="n">
+        <v>9</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
+        <v>16</v>
+      </c>
+      <c r="X37" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>7</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>11</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>9</v>
+      </c>
+      <c r="J38" t="n">
+        <v>7</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4</v>
+      </c>
+      <c r="L38" t="n">
+        <v>14</v>
+      </c>
+      <c r="M38" t="n">
+        <v>8</v>
+      </c>
+      <c r="N38" t="n">
+        <v>6</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2</v>
+      </c>
+      <c r="P38" t="n">
+        <v>4</v>
+      </c>
+      <c r="V38" t="n">
+        <v>11</v>
+      </c>
+      <c r="W38" t="n">
+        <v>24</v>
+      </c>
+      <c r="X38" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Extended Data 3e — Barnes maze probe trial: latency (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Statistical test: Kruskal-Wallis with Dunn's multiple comparisons</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Row = condition/trial; values are individual animals, WT, then 5xFAD-EGFP, then 5xFAD-SV2A, in the order plotted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="n">
+        <v>18</v>
+      </c>
+      <c r="C44" t="n">
+        <v>23</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="n">
+        <v>90</v>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="n">
+        <v>9</v>
+      </c>
+      <c r="C46" t="n">
+        <v>37</v>
+      </c>
+      <c r="D46" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="n">
+        <v>68</v>
+      </c>
+      <c r="C47" t="n">
+        <v>26</v>
+      </c>
+      <c r="D47" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="n">
+        <v>15</v>
+      </c>
+      <c r="D49" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="n">
+        <v>10</v>
+      </c>
+      <c r="D50" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="n">
+        <v>11</v>
+      </c>
+      <c r="D52" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>Extended Data 3f — Barnes maze probe trial: errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Statistical test: Kruskal-Wallis with Dunn's multiple comparisons</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">      e   mIPSC inter-event interval, cumulative distribution</t>
+          <t>Row = condition/trial; values are individual animals, WT, then 5xFAD-EGFP, then 5xFAD-SV2A, in the order plotted.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      f   sIPSC / mIPSC amplitude (pA)</t>
-        </is>
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="n">
+        <v>17</v>
+      </c>
+      <c r="C59" t="n">
+        <v>9</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      g   sIPSC amplitude, cumulative distribution</t>
-        </is>
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="n">
+        <v>40</v>
+      </c>
+      <c r="C60" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      h   mIPSC amplitude, cumulative distribution</t>
-        </is>
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="n">
+        <v>4</v>
+      </c>
+      <c r="C61" t="n">
+        <v>7</v>
+      </c>
+      <c r="D61" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      i   sIPSC / mIPSC rise time (ms)</t>
-        </is>
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="n">
+        <v>20</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      j   sIPSC rise time, cumulative distribution</t>
-        </is>
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      k   mIPSC rise time, cumulative distribution</t>
-        </is>
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="n">
+        <v>7</v>
+      </c>
+      <c r="D64" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Figure 3</t>
-        </is>
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      c   Seizures per 24 h of recording, baseline (weeks 1-3)</t>
-        </is>
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      d   % of recorded days without a convulsive seizure, baseline</t>
-        </is>
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="n">
+        <v>9</v>
+      </c>
+      <c r="D67" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      e   All seizures per 24 h, by baseline week</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      f   Time to first convulsive seizure, baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      g   Cumulative convulsive seizure burden (min), baseline days 1-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      h   Mean seizure duration (s), whole recording</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      i   Average behavioural seizure grade during status epilepticus</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      j   Cumulative behavioural seizure grade during SE</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      k   Cumulative SE grade vs chronic seizure rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Figure 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      c   Interictal spikes per animal-hour, baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      d   Mean interictal spike duration (s), baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      e   Inter-spike-interval probability density (ISIs pooled within group)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      f   Inter-spike-interval cumulative distribution (pooled within group)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Figure 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      a   All seizures per animal-hour, by recording day</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      b   % days convulsive-free, baseline vs levetiracetam</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      c   Convulsive seizures per 24 h, baseline vs levetiracetam</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      d   Non-convulsive seizures per 24 h, baseline vs levetiracetam</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      e   Mean convulsive seizure duration (s), baseline vs levetiracetam</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      f   Mean non-convulsive seizure duration (s), baseline vs levetiracetam</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      g   Interictal spikes per animal-hour, baseline vs levetiracetam</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      h   ISI cumulative distribution, EGFP, baseline vs LEV</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      h   ISI cumulative distribution, SV2A, baseline vs LEV</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      i   Mean spike duration (s), baseline vs levetiracetam</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Figure 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      b   Object location test — exploration time (s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      c   Object location test — head entries</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      d   Object location test — discrimination index</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      f   Novel object recognition — exploration time (s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      g   Novel object recognition — head entries</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      h   Novel object recognition — discrimination index</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      j   Nest-building score (Deacon protocol)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      l   Open field — time mobile (s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      m   Open field — centre entries</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      n   Open field — time in centre (s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      o   Open field — time in centre (% of mobile time)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Extended Data 1 (AD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      c   Interictal spikes per animal-hour, by recording day (col 1 = day, then animals 1-4, then cohort mean)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      d   Interictal spikes per animal-hour, by week (rows = animals 1-4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      -   Seizures detected in the AD cohort (not plotted; quoted in the text)</t>
-        </is>
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="n">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Extended Data 1 (AD)c — Interictal spikes per animal-hour, by recording day (col 1 = day, then animals 1-4, then cohort mean)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Statistical test: Linear regression</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Curve data as plotted; columns as in the figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>6.262</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.368</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.463</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.368</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4.11525</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="n">
+        <v>14.516</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4.934</v>
+      </c>
+      <c r="D5" t="n">
+        <v>21.244</v>
+      </c>
+      <c r="E5" t="n">
+        <v>15.821</v>
+      </c>
+      <c r="F5" t="n">
+        <v>14.12875</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="n">
+        <v>13.171</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.415</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10.569</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10.732</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9.47175</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="n">
+        <v>9.093999999999999</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.974</v>
+      </c>
+      <c r="D7" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="E7" t="n">
+        <v>13.663</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9.97775</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5.906</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2.148</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.502</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6.361</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4.72925</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7.762</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5.857</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.095</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.476</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6.0475</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8.667</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8.667</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6.66675</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="n">
+        <v>22.841</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5.675</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10.365</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12.89775</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" t="n">
+        <v>20.533</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>12.466</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9.666</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12.11625</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" t="n">
+        <v>17.841</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5.565</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7.816</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5.352</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9.1435</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" t="n">
+        <v>19.934</v>
+      </c>
+      <c r="C14" t="n">
+        <v>13.934</v>
+      </c>
+      <c r="D14" t="n">
+        <v>12.041</v>
+      </c>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>12.97725</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" t="n">
+        <v>18.952</v>
+      </c>
+      <c r="C15" t="n">
+        <v>10.285</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8.856999999999999</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10.85675</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" t="n">
+        <v>23.046</v>
+      </c>
+      <c r="C16" t="n">
+        <v>13.022</v>
+      </c>
+      <c r="D16" t="n">
+        <v>17.563</v>
+      </c>
+      <c r="E16" t="n">
+        <v>18.248</v>
+      </c>
+      <c r="F16" t="n">
+        <v>17.96975</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" t="n">
+        <v>17.804</v>
+      </c>
+      <c r="C17" t="n">
+        <v>9.989000000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7.565</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11.995</v>
+      </c>
+      <c r="F17" t="n">
+        <v>11.83825</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" t="n">
+        <v>18.245</v>
+      </c>
+      <c r="C18" t="n">
+        <v>9.952</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5.906</v>
+      </c>
+      <c r="E18" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="F18" t="n">
+        <v>11.63075</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" t="n">
+        <v>15.701</v>
+      </c>
+      <c r="C19" t="n">
+        <v>13.126</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.389</v>
+      </c>
+      <c r="E19" t="n">
+        <v>19.626</v>
+      </c>
+      <c r="F19" t="n">
+        <v>13.2105</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" t="n">
+        <v>18.262</v>
+      </c>
+      <c r="C20" t="n">
+        <v>16.491</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.609</v>
+      </c>
+      <c r="E20" t="n">
+        <v>17.587</v>
+      </c>
+      <c r="F20" t="n">
+        <v>14.48725</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" t="n">
+        <v>27.593</v>
+      </c>
+      <c r="C21" t="n">
+        <v>30.831</v>
+      </c>
+      <c r="D21" t="n">
+        <v>11.609</v>
+      </c>
+      <c r="E21" t="n">
+        <v>16.026</v>
+      </c>
+      <c r="F21" t="n">
+        <v>21.51475</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="C22" t="n">
+        <v>24.639</v>
+      </c>
+      <c r="D22" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="E22" t="n">
+        <v>14.841</v>
+      </c>
+      <c r="F22" t="n">
+        <v>17.1975</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" t="n">
+        <v>17.414</v>
+      </c>
+      <c r="C23" t="n">
+        <v>26.699</v>
+      </c>
+      <c r="D23" t="n">
+        <v>19.414</v>
+      </c>
+      <c r="E23" t="n">
+        <v>13.327</v>
+      </c>
+      <c r="F23" t="n">
+        <v>19.2135</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" t="n">
+        <v>18.269</v>
+      </c>
+      <c r="C24" t="n">
+        <v>31.302</v>
+      </c>
+      <c r="D24" t="n">
+        <v>9.249000000000001</v>
+      </c>
+      <c r="E24" t="n">
+        <v>11.848</v>
+      </c>
+      <c r="F24" t="n">
+        <v>17.667</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Extended Data 1 (AD)d — Interictal spikes per animal-hour, by week (rows = animals 1-4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Statistical test: Descriptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Curve data as plotted; columns as in the figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>9.577999999999999</v>
+      </c>
+      <c r="C30" t="n">
+        <v>20.083</v>
+      </c>
+      <c r="D30" t="n">
+        <v>19.27</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>3.804</v>
+      </c>
+      <c r="C31" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="D31" t="n">
+        <v>21.907</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>10.199</v>
+      </c>
+      <c r="C32" t="n">
+        <v>10.904</v>
+      </c>
+      <c r="D32" t="n">
+        <v>9.345000000000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>9.228</v>
+      </c>
+      <c r="C33" t="n">
+        <v>9.911</v>
+      </c>
+      <c r="D33" t="n">
+        <v>15.045</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Extended Data 1 (AD)- — Seizures detected in the AD cohort (not plotted; quoted in the text)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Statistical test: Descriptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Confidence &gt;= 0.5; every event visually confirmed. Recording 462 h per animal (1,847 animal-hours).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>convulsive</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>non-convulsive</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AD animal 2</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AD animal 2</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>3</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AD animal 4</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1219,7 +4011,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Row = condition/region; values are individual animals, EGFP block then SV2A block, in the order plotted.</t>
+          <t>Row = condition/trial; values are individual animals, EGFP block then SV2A block, in the order plotted.</t>
         </is>
       </c>
     </row>
@@ -1424,7 +4216,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Row = condition/region; values are individual animals, EGFP block then SV2A block, in the order plotted.</t>
+          <t>Row = condition/trial; values are individual animals, EGFP block then SV2A block, in the order plotted.</t>
         </is>
       </c>
     </row>
@@ -1675,7 +4467,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Row = condition/region; values are individual animals, EGFP block then SV2A block, in the order plotted.</t>
+          <t>Row = condition/trial; values are individual animals, EGFP block then SV2A block, in the order plotted.</t>
         </is>
       </c>
     </row>
@@ -11019,7 +13811,7 @@
     <row r="1220">
       <c r="A1220" s="2" t="inlineStr">
         <is>
-          <t>Row = condition/region; values are individual animals, EGFP block then SV2A block, in the order plotted.</t>
+          <t>Row = condition/trial; values are individual animals, EGFP block then SV2A block, in the order plotted.</t>
         </is>
       </c>
     </row>
@@ -20465,7 +23257,7 @@
     <row r="2437">
       <c r="A2437" s="2" t="inlineStr">
         <is>
-          <t>Row = condition/region; values are individual animals, EGFP block then SV2A block, in the order plotted.</t>
+          <t>Row = condition/trial; values are individual animals, EGFP block then SV2A block, in the order plotted.</t>
         </is>
       </c>
     </row>
@@ -42859,7 +45651,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Row = condition/region; values are individual animals, EGFP block then SV2A block, in the order plotted.</t>
+          <t>Row = condition/trial; values are individual animals, EGFP block then SV2A block, in the order plotted.</t>
         </is>
       </c>
     </row>
@@ -43038,7 +45830,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Row = condition/region; values are individual animals, EGFP block then SV2A block, in the order plotted.</t>
+          <t>Row = condition/trial; values are individual animals, EGFP block then SV2A block, in the order plotted.</t>
         </is>
       </c>
     </row>
@@ -43341,7 +46133,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Row = condition/region; values are individual animals, EGFP block then SV2A block, in the order plotted.</t>
+          <t>Row = condition/trial; values are individual animals, EGFP block then SV2A block, in the order plotted.</t>
         </is>
       </c>
     </row>
@@ -43520,7 +46312,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Row = condition/region; values are individual animals, EGFP block then SV2A block, in the order plotted.</t>
+          <t>Row = condition/trial; values are individual animals, EGFP block then SV2A block, in the order plotted.</t>
         </is>
       </c>
     </row>
@@ -44424,7 +47216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:AE63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -44462,598 +47254,1798 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Extended Data 1 (AD)c — Interictal spikes per animal-hour, by recording day (col 1 = day, then animals 1-4, then cohort mean)</t>
+          <t>Figure 7a — Open field distance (m), WT vs 5xFAD at baseline (2 columns)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Statistical test: Linear regression</t>
+          <t>Statistical test: Unpaired t-test</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>WT</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>5xFAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="B4" t="n">
+        <v>47.004</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>58.832</v>
+      </c>
+      <c r="B5" t="n">
+        <v>52.855</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>58.351</v>
+      </c>
+      <c r="B6" t="n">
+        <v>77.035</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113.105</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102.908</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>73.44799999999999</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83.94199999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>79.497</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58.485</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113.115</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78.187</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>67.65600000000001</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56.985</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>84.893</v>
+      </c>
+      <c r="B12" t="n">
+        <v>69.46599999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>62.492</v>
+      </c>
+      <c r="B13" t="n">
+        <v>86.908</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>68.878</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>62.037</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>49.603</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>78.28400000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>71.18000000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>75.907</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>65.593</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>104.415</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>70.048</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>57.205</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Figure 7b — Open field distance (m) after treatment (columns: WT, 5xFAD-EGFP, 5xFAD-SV2A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Statistical test: Kruskal-Wallis with Dunn's multiple comparisons</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>WT</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>5xFAD-EGFP</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>5xFAD-SV2A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>39.797</v>
+      </c>
+      <c r="B29" t="n">
+        <v>193.632</v>
+      </c>
+      <c r="C29" t="n">
+        <v>69.09099999999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>39.67</v>
+      </c>
+      <c r="B30" t="n">
+        <v>68.205</v>
+      </c>
+      <c r="C30" t="n">
+        <v>84.896</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>63.121</v>
+      </c>
+      <c r="B31" t="n">
+        <v>135.332</v>
+      </c>
+      <c r="C31" t="n">
+        <v>116.174</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>80.026</v>
+      </c>
+      <c r="B32" t="n">
+        <v>164.409</v>
+      </c>
+      <c r="C32" t="n">
+        <v>51.287</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>55.25</v>
+      </c>
+      <c r="B33" t="n">
+        <v>125.548</v>
+      </c>
+      <c r="C33" t="n">
+        <v>91.178</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="B34" t="n">
+        <v>129.529</v>
+      </c>
+      <c r="C34" t="n">
+        <v>71.372</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>83.801</v>
+      </c>
+      <c r="B35" t="n">
+        <v>222.724</v>
+      </c>
+      <c r="C35" t="n">
+        <v>118.077</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>55.69</v>
+      </c>
+      <c r="C36" t="n">
+        <v>80.227</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>64.94199999999999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>100.294</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>51.09</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Figure 7c — Time in centre (fraction of total), pre vs post treatment (rows Pre/Post; columns are animals, WT then 5xFAD-EGFP then 5xFAD-SV2A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Statistical test: Kruskal-Wallis with Dunn's multiple comparisons</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Row = condition/trial; values are individual animals, WT, then 5xFAD-EGFP, then 5xFAD-SV2A, in the order plotted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.0872</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.0847</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.1579</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.1406</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.09520000000000001</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.2547</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.2315</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.2139</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.2136</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.2205</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0.2204</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.1588</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.2317</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0.1884</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.1285</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.1694</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.1104</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.2251</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.1062</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.2438</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.07770000000000001</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.1636</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.2519</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.1275</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.0379</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.2092</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.2521</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0.2558</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0.1766</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.1557</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Figure 7d — Barnes maze, change in AUC of primary latency</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Statistical test: Kruskal-Wallis with Dunn's multiple comparisons</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Row = condition/trial; values are individual animals, WT, then 5xFAD-EGFP, then 5xFAD-SV2A, in the order plotted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>-258.5</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-25.5</v>
+      </c>
+      <c r="D51" t="n">
+        <v>8</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-196.5</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-80</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-158</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-72.5</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-103.5</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="K51" t="n">
+        <v>65</v>
+      </c>
+      <c r="L51" t="n">
+        <v>99</v>
+      </c>
+      <c r="M51" t="n">
+        <v>354</v>
+      </c>
+      <c r="N51" t="n">
+        <v>218</v>
+      </c>
+      <c r="S51" t="n">
+        <v>124</v>
+      </c>
+      <c r="T51" t="n">
+        <v>114</v>
+      </c>
+      <c r="U51" t="n">
+        <v>-38</v>
+      </c>
+      <c r="V51" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="W51" t="n">
+        <v>58</v>
+      </c>
+      <c r="X51" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>-161.5</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-165.5</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>-26</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>Figure 7e — Barnes maze, change in AUC of total latency</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Statistical test: Kruskal-Wallis with Dunn's multiple comparisons</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Row = condition/trial; values are individual animals, WT, then 5xFAD-EGFP, then 5xFAD-SV2A, in the order plotted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>-533</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>-269.5</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-40</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-75.5</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-384</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-116.5</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-289.5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-95</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-249.5</v>
+      </c>
+      <c r="J57" t="n">
+        <v>33</v>
+      </c>
+      <c r="K57" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-362.5</v>
+      </c>
+      <c r="M57" t="n">
+        <v>295.5</v>
+      </c>
+      <c r="N57" t="n">
+        <v>216</v>
+      </c>
+      <c r="S57" t="n">
+        <v>117</v>
+      </c>
+      <c r="T57" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="U57" t="n">
+        <v>-36.5</v>
+      </c>
+      <c r="V57" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W57" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="X57" t="n">
+        <v>127</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>-386</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-203.5</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-254.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>Figure 7f — Barnes maze, change in AUC of total errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Statistical test: Kruskal-Wallis with Dunn's multiple comparisons</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Row = condition/trial; values are individual animals, WT, then 5xFAD-EGFP, then 5xFAD-SV2A, in the order plotted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>-6.5</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>-29.5</v>
+      </c>
+      <c r="C63" t="n">
+        <v>9</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-13</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-24</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-45.5</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-37</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-37.5</v>
+      </c>
+      <c r="J63" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="K63" t="n">
+        <v>33</v>
+      </c>
+      <c r="L63" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M63" t="n">
+        <v>10</v>
+      </c>
+      <c r="N63" t="n">
+        <v>9</v>
+      </c>
+      <c r="S63" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="T63" t="n">
+        <v>7</v>
+      </c>
+      <c r="U63" t="n">
+        <v>7</v>
+      </c>
+      <c r="V63" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="W63" t="n">
+        <v>20</v>
+      </c>
+      <c r="X63" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>-44</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-28</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>-20.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AE54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Extended Data 2a — Object location: exploration time (s), familiar vs displaced</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Statistical test: Kruskal-Wallis with Dunn's multiple comparisons</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Curve data as plotted; columns as in the figure.</t>
+          <t>Row = condition/trial; values are individual animals, WT, then 5xFAD-EGFP, then 5xFAD-SV2A, in the order plotted.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Familiar object</t>
+        </is>
       </c>
       <c r="B4" t="n">
-        <v>6.262</v>
+        <v>27.9</v>
       </c>
       <c r="C4" t="n">
-        <v>3.368</v>
+        <v>23.7</v>
       </c>
       <c r="D4" t="n">
-        <v>3.463</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>3.368</v>
+        <v>33.4</v>
       </c>
       <c r="F4" t="n">
-        <v>4.11525</v>
+        <v>25.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K4" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="L4" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="N4" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="V4" t="n">
+        <v>34</v>
+      </c>
+      <c r="W4" t="n">
+        <v>27</v>
+      </c>
+      <c r="X4" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>26.3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Displaced object</t>
+        </is>
       </c>
       <c r="B5" t="n">
-        <v>14.516</v>
+        <v>33.3</v>
       </c>
       <c r="C5" t="n">
-        <v>4.934</v>
+        <v>36.3</v>
       </c>
       <c r="D5" t="n">
-        <v>21.244</v>
+        <v>22.8</v>
       </c>
       <c r="E5" t="n">
-        <v>15.821</v>
+        <v>29.9</v>
       </c>
       <c r="F5" t="n">
-        <v>14.12875</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="n">
-        <v>13.171</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3.415</v>
-      </c>
-      <c r="D6" t="n">
-        <v>10.569</v>
-      </c>
-      <c r="E6" t="n">
-        <v>10.732</v>
-      </c>
-      <c r="F6" t="n">
-        <v>9.47175</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="n">
-        <v>9.093999999999999</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2.974</v>
-      </c>
-      <c r="D7" t="n">
-        <v>14.18</v>
-      </c>
-      <c r="E7" t="n">
-        <v>13.663</v>
-      </c>
-      <c r="F7" t="n">
-        <v>9.97775</v>
+        <v>22.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>65</v>
+      </c>
+      <c r="J5" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>118.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>87</v>
+      </c>
+      <c r="N5" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="O5" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>74</v>
+      </c>
+      <c r="R5" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="V5" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="W5" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>46.4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="n">
-        <v>5.906</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2.148</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4.502</v>
-      </c>
-      <c r="E8" t="n">
-        <v>6.361</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4.72925</v>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Extended Data 2b — Object location: head entries, familiar vs displaced</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="n">
-        <v>7.762</v>
-      </c>
-      <c r="C9" t="n">
-        <v>5.857</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6.095</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.476</v>
-      </c>
-      <c r="F9" t="n">
-        <v>6.0475</v>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Statistical test: Kruskal-Wallis with Dunn's multiple comparisons</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Row = condition/trial; values are individual animals, WT, then 5xFAD-EGFP, then 5xFAD-SV2A, in the order plotted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Familiar object</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>26</v>
+      </c>
+      <c r="C11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>28</v>
+      </c>
+      <c r="F11" t="n">
+        <v>16</v>
+      </c>
+      <c r="G11" t="n">
+        <v>17</v>
+      </c>
+      <c r="H11" t="n">
+        <v>23</v>
+      </c>
+      <c r="I11" t="n">
+        <v>49</v>
+      </c>
+      <c r="J11" t="n">
+        <v>16</v>
+      </c>
+      <c r="K11" t="n">
+        <v>35</v>
+      </c>
+      <c r="L11" t="n">
+        <v>69</v>
+      </c>
+      <c r="M11" t="n">
+        <v>61</v>
+      </c>
+      <c r="N11" t="n">
+        <v>93</v>
+      </c>
+      <c r="O11" t="n">
+        <v>12</v>
+      </c>
+      <c r="P11" t="n">
         <v>7</v>
       </c>
-      <c r="B10" t="n">
-        <v>8.667</v>
-      </c>
-      <c r="C10" t="n">
-        <v>8.667</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="F10" t="n">
-        <v>6.66675</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" t="n">
-        <v>22.841</v>
-      </c>
-      <c r="C11" t="n">
-        <v>5.675</v>
-      </c>
-      <c r="D11" t="n">
-        <v>10.365</v>
-      </c>
-      <c r="E11" t="n">
-        <v>12.71</v>
-      </c>
-      <c r="F11" t="n">
-        <v>12.89775</v>
+      <c r="Q11" t="n">
+        <v>69</v>
+      </c>
+      <c r="R11" t="n">
+        <v>11</v>
+      </c>
+      <c r="V11" t="n">
+        <v>47</v>
+      </c>
+      <c r="W11" t="n">
+        <v>35</v>
+      </c>
+      <c r="X11" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>33</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Displaced object</t>
+        </is>
       </c>
       <c r="B12" t="n">
-        <v>20.533</v>
+        <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>5.8</v>
+        <v>33</v>
       </c>
       <c r="D12" t="n">
-        <v>12.466</v>
+        <v>29</v>
       </c>
       <c r="E12" t="n">
-        <v>9.666</v>
+        <v>37</v>
       </c>
       <c r="F12" t="n">
-        <v>12.11625</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="n">
-        <v>17.841</v>
-      </c>
-      <c r="C13" t="n">
-        <v>5.565</v>
-      </c>
-      <c r="D13" t="n">
-        <v>7.816</v>
-      </c>
-      <c r="E13" t="n">
-        <v>5.352</v>
-      </c>
-      <c r="F13" t="n">
-        <v>9.1435</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="n">
-        <v>19.934</v>
-      </c>
-      <c r="C14" t="n">
-        <v>13.934</v>
-      </c>
-      <c r="D14" t="n">
-        <v>12.041</v>
-      </c>
-      <c r="E14" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" t="n">
-        <v>12.97725</v>
+        <v>36</v>
+      </c>
+      <c r="G12" t="n">
+        <v>31</v>
+      </c>
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>64</v>
+      </c>
+      <c r="J12" t="n">
+        <v>61</v>
+      </c>
+      <c r="K12" t="n">
+        <v>39</v>
+      </c>
+      <c r="L12" t="n">
+        <v>89</v>
+      </c>
+      <c r="M12" t="n">
+        <v>61</v>
+      </c>
+      <c r="N12" t="n">
+        <v>103</v>
+      </c>
+      <c r="O12" t="n">
+        <v>33</v>
+      </c>
+      <c r="P12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>81</v>
+      </c>
+      <c r="R12" t="n">
+        <v>56</v>
+      </c>
+      <c r="V12" t="n">
+        <v>89</v>
+      </c>
+      <c r="W12" t="n">
+        <v>68</v>
+      </c>
+      <c r="X12" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>41</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>72</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>76</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" t="n">
-        <v>18.952</v>
-      </c>
-      <c r="C15" t="n">
-        <v>10.285</v>
-      </c>
-      <c r="D15" t="n">
-        <v>8.856999999999999</v>
-      </c>
-      <c r="E15" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="F15" t="n">
-        <v>10.85675</v>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Extended Data 2c — Object location: discrimination index (columns: WT-Sham, 5xFAD-EGFP, 5xFAD-SV2A)</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" t="n">
-        <v>23.046</v>
-      </c>
-      <c r="C16" t="n">
-        <v>13.022</v>
-      </c>
-      <c r="D16" t="n">
-        <v>17.563</v>
-      </c>
-      <c r="E16" t="n">
-        <v>18.248</v>
-      </c>
-      <c r="F16" t="n">
-        <v>17.96975</v>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Statistical test: Kruskal-Wallis with Dunn's multiple comparisons</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" t="n">
-        <v>17.804</v>
-      </c>
-      <c r="C17" t="n">
-        <v>9.989000000000001</v>
-      </c>
-      <c r="D17" t="n">
-        <v>7.565</v>
-      </c>
-      <c r="E17" t="n">
-        <v>11.995</v>
-      </c>
-      <c r="F17" t="n">
-        <v>11.83825</v>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>WT</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>5xFAD-EGFP</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>5xFAD-SV2A</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>15</v>
+        <v>0.08823528999999999</v>
       </c>
       <c r="B18" t="n">
-        <v>18.245</v>
+        <v>0.38992974</v>
       </c>
       <c r="C18" t="n">
-        <v>9.952</v>
-      </c>
-      <c r="D18" t="n">
-        <v>5.906</v>
-      </c>
-      <c r="E18" t="n">
-        <v>12.42</v>
-      </c>
-      <c r="F18" t="n">
-        <v>11.63075</v>
+        <v>0.54454119</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>16</v>
+        <v>0.21</v>
       </c>
       <c r="B19" t="n">
-        <v>15.701</v>
+        <v>0.29271917</v>
       </c>
       <c r="C19" t="n">
-        <v>13.126</v>
-      </c>
-      <c r="D19" t="n">
-        <v>4.389</v>
-      </c>
-      <c r="E19" t="n">
-        <v>19.626</v>
-      </c>
-      <c r="F19" t="n">
-        <v>13.2105</v>
+        <v>0.32075472</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>17</v>
+        <v>0.46623794</v>
       </c>
       <c r="B20" t="n">
-        <v>18.262</v>
+        <v>0.25048294</v>
       </c>
       <c r="C20" t="n">
-        <v>16.491</v>
-      </c>
-      <c r="D20" t="n">
-        <v>5.609</v>
-      </c>
-      <c r="E20" t="n">
-        <v>17.587</v>
-      </c>
-      <c r="F20" t="n">
-        <v>14.48725</v>
+        <v>0.4567474</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>18</v>
+        <v>-0.0552923</v>
       </c>
       <c r="B21" t="n">
-        <v>27.593</v>
+        <v>0.21189591</v>
       </c>
       <c r="C21" t="n">
-        <v>30.831</v>
-      </c>
-      <c r="D21" t="n">
-        <v>11.609</v>
-      </c>
-      <c r="E21" t="n">
-        <v>16.026</v>
-      </c>
-      <c r="F21" t="n">
-        <v>21.51475</v>
+        <v>0.41265345</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>19</v>
+        <v>-0.06918240000000001</v>
       </c>
       <c r="B22" t="n">
-        <v>19.43</v>
+        <v>0.54152824</v>
       </c>
       <c r="C22" t="n">
-        <v>24.639</v>
-      </c>
-      <c r="D22" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="E22" t="n">
-        <v>14.841</v>
-      </c>
-      <c r="F22" t="n">
-        <v>17.1975</v>
+        <v>0.40134745</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20</v>
+        <v>0.46737213</v>
       </c>
       <c r="B23" t="n">
-        <v>17.414</v>
+        <v>-0.0662461</v>
       </c>
       <c r="C23" t="n">
-        <v>26.699</v>
-      </c>
-      <c r="D23" t="n">
-        <v>19.414</v>
-      </c>
-      <c r="E23" t="n">
-        <v>13.327</v>
-      </c>
-      <c r="F23" t="n">
-        <v>19.2135</v>
+        <v>0.25545171</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>21</v>
+        <v>0.52470588</v>
       </c>
       <c r="B24" t="n">
-        <v>18.269</v>
+        <v>0.76283186</v>
       </c>
       <c r="C24" t="n">
-        <v>31.302</v>
-      </c>
-      <c r="D24" t="n">
-        <v>9.249000000000001</v>
-      </c>
-      <c r="E24" t="n">
-        <v>11.848</v>
-      </c>
-      <c r="F24" t="n">
-        <v>17.667</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>Extended Data 1 (AD)d — Interictal spikes per animal-hour, by week (rows = animals 1-4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Statistical test: Descriptive</t>
-        </is>
+        <v>0.43269231</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>0.1130137</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.30179641</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>0.70068027</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.27647868</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Curve data as plotted; columns as in the figure.</t>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Extended Data 2d — Novel object: exploration time (s), familiar vs novel</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="n">
-        <v>9.577999999999999</v>
-      </c>
-      <c r="C30" t="n">
-        <v>20.083</v>
-      </c>
-      <c r="D30" t="n">
-        <v>19.27</v>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Statistical test: Kruskal-Wallis with Dunn's multiple comparisons</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="n">
-        <v>3.804</v>
-      </c>
-      <c r="C31" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="D31" t="n">
-        <v>21.907</v>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Row = condition/trial; values are individual animals, WT, then 5xFAD-EGFP, then 5xFAD-SV2A, in the order plotted.</t>
+        </is>
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Familiar object</t>
+        </is>
+      </c>
       <c r="B32" t="n">
-        <v>10.199</v>
+        <v>3.3</v>
       </c>
       <c r="C32" t="n">
-        <v>10.904</v>
+        <v>11.2</v>
       </c>
       <c r="D32" t="n">
-        <v>9.345000000000001</v>
+        <v>0.9</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="J32" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L32" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N32" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="V32" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="X32" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>35</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>28.5</v>
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Novel object</t>
+        </is>
+      </c>
       <c r="B33" t="n">
-        <v>9.228</v>
+        <v>24.7</v>
       </c>
       <c r="C33" t="n">
-        <v>9.911</v>
+        <v>18.7</v>
       </c>
       <c r="D33" t="n">
-        <v>15.045</v>
+        <v>6.1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="G33" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="H33" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="I33" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="K33" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="L33" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="N33" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="O33" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P33" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="V33" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="W33" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="X33" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>72</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>63.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Extended Data 1 (AD)- — Seizures detected in the AD cohort (not plotted; quoted in the text)</t>
+          <t>Extended Data 2e — Novel object: head entries, familiar vs novel</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Statistical test: Descriptive</t>
+          <t>Statistical test: Kruskal-Wallis with Dunn's multiple comparisons</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Confidence &gt;= 0.5; every event visually confirmed. Recording 462 h per animal (1,847 animal-hours).</t>
+          <t>Row = condition/trial; values are individual animals, WT, then 5xFAD-EGFP, then 5xFAD-SV2A, in the order plotted.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>animal</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>week</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>convulsive</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>non-convulsive</t>
-        </is>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Familiar object</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" t="n">
+        <v>12</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="n">
+        <v>10</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22</v>
+      </c>
+      <c r="G39" t="n">
+        <v>10</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" t="n">
+        <v>32</v>
+      </c>
+      <c r="J39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K39" t="n">
+        <v>21</v>
+      </c>
+      <c r="L39" t="n">
+        <v>57</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>57</v>
+      </c>
+      <c r="O39" t="n">
+        <v>9</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>74</v>
+      </c>
+      <c r="R39" t="n">
+        <v>14</v>
+      </c>
+      <c r="V39" t="n">
+        <v>40</v>
+      </c>
+      <c r="W39" t="n">
+        <v>43</v>
+      </c>
+      <c r="X39" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>33</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AD animal 2</t>
+          <t>Novel object</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>AD animal 2</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>3</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>AD animal 4</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>3</v>
-      </c>
-      <c r="C42" t="n">
-        <v>2</v>
-      </c>
-      <c r="D42" t="n">
-        <v>11</v>
+        <v>7</v>
+      </c>
+      <c r="E40" t="n">
+        <v>36</v>
+      </c>
+      <c r="F40" t="n">
+        <v>32</v>
+      </c>
+      <c r="G40" t="n">
+        <v>31</v>
+      </c>
+      <c r="H40" t="n">
+        <v>22</v>
+      </c>
+      <c r="I40" t="n">
+        <v>30</v>
+      </c>
+      <c r="J40" t="n">
+        <v>19</v>
+      </c>
+      <c r="K40" t="n">
+        <v>23</v>
+      </c>
+      <c r="L40" t="n">
+        <v>68</v>
+      </c>
+      <c r="M40" t="n">
+        <v>21</v>
+      </c>
+      <c r="N40" t="n">
+        <v>78</v>
+      </c>
+      <c r="O40" t="n">
+        <v>31</v>
+      </c>
+      <c r="P40" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>73</v>
+      </c>
+      <c r="R40" t="n">
+        <v>12</v>
+      </c>
+      <c r="V40" t="n">
+        <v>61</v>
+      </c>
+      <c r="W40" t="n">
+        <v>56</v>
+      </c>
+      <c r="X40" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Extended Data 2f — Novel object: discrimination index (columns: WT-Sham, 5xFAD-EGFP, 5xFAD-SV2A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Statistical test: Kruskal-Wallis with Dunn's multiple comparisons</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>WT</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>5xFAD-EGFP</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>5xFAD-SV2A</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>0.76428571</v>
+      </c>
+      <c r="B46" t="n">
+        <v>0.17744807</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.42418033</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>0.25083612</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0.96756757</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.22546012</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>0.74285714</v>
+      </c>
+      <c r="B48" t="n">
+        <v>0.3769339</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.09140520000000001</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>0.75847458</v>
+      </c>
+      <c r="B49" t="n">
+        <v>0.76657825</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.71799028</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>0.30232558</v>
+      </c>
+      <c r="B50" t="n">
+        <v>0.88034188</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.34579439</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>0.82173913</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0.1440678</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.66292135</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>0.98571429</v>
+      </c>
+      <c r="B52" t="n">
+        <v>0.00813008</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.80783818</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>0.03095238</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.38043478</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>0.69924812</v>
       </c>
     </row>
   </sheetData>
